--- a/src/exportToExcel/Certificate.xlsx
+++ b/src/exportToExcel/Certificate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,48 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>32fba54a-86e7-4527-abb1-0eac2f3ac48a</t>
+  </si>
+  <si>
+    <t>A12345678O</t>
+  </si>
+  <si>
+    <t>eda@yahoo.com</t>
+  </si>
+  <si>
+    <t>2022-07-08</t>
+  </si>
+  <si>
+    <t>c37c2792-56d9-4471-a90a-549493a7e0ae</t>
+  </si>
+  <si>
+    <t>E12345769P</t>
+  </si>
+  <si>
+    <t>edaisaku0@gmail.com</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>629d0223-6119-4e78-9b1b-466cedd12761</t>
+  </si>
+  <si>
+    <t>E82345769P</t>
+  </si>
+  <si>
+    <t>edaisaku@gmail.com</t>
+  </si>
+  <si>
+    <t>TH</t>
   </si>
 </sst>
 </file>
@@ -454,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -510,6 +552,32 @@
         <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -562,7 +630,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -595,6 +663,32 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -603,7 +697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -636,6 +730,32 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/src/exportToExcel/Certificate.xlsx
+++ b/src/exportToExcel/Certificate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,72 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>32fba54a-86e7-4527-abb1-0eac2f3ac48a</t>
+  </si>
+  <si>
+    <t>A12345678O</t>
+  </si>
+  <si>
+    <t>eda@yahoo.com</t>
+  </si>
+  <si>
+    <t>2022-07-08</t>
+  </si>
+  <si>
+    <t>86710861-2344-40a1-ab8e-915789db2f87</t>
+  </si>
+  <si>
+    <t>A12345678P</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>9bd33e64-dd33-4ef8-8ef4-edde7f870ee3</t>
+  </si>
+  <si>
+    <t>A12395678P</t>
+  </si>
+  <si>
+    <t>tes1t@gmail.com</t>
+  </si>
+  <si>
+    <t>c37c2792-56d9-4471-a90a-549493a7e0ae</t>
+  </si>
+  <si>
+    <t>E12345769P</t>
+  </si>
+  <si>
+    <t>edaisaku0@gmail.com</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>629d0223-6119-4e78-9b1b-466cedd12761</t>
+  </si>
+  <si>
+    <t>E82345769P</t>
+  </si>
+  <si>
+    <t>edaisaku@gmail.com</t>
+  </si>
+  <si>
+    <t>TH</t>
   </si>
 </sst>
 </file>
@@ -454,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -510,6 +576,84 @@
         <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -562,7 +706,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -595,6 +739,32 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -603,7 +773,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -636,6 +806,32 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
